--- a/ig/DM_FINESS_New/ValueSet-jdv-j375-ordre.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-j375-ordre.xlsx
@@ -30,7 +30,7 @@
     <t>Identifier</t>
   </si>
   <si>
-    <t>OID:1.2.250.1.213.1.6.1.381</t>
+    <t>OID:1.2.250.1.213.1.6.1.389</t>
   </si>
   <si>
     <t>Version</t>
